--- a/member3_deliverables/Testing_Workbook.xlsx
+++ b/member3_deliverables/Testing_Workbook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MC-DC Evidence" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MC-DC Evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L125</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L169 (TaskSwitchingBasics); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L138</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L183 (TaskSwitchingWithIntegerIndex); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L152</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L198 (ErrorToStringMapping); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L160</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L206 (StartFlightTaskAutoModes); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L209</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L265 (StartFlightTaskPositionControlModes); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L236</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L295 (StartFlightTaskAltitudeControlModes); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L263</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L325 (StartFlightTaskAltitudeCruiseAndDescend); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L282</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L345 (StartFlightTaskUnmatchedTaskFallback); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L302</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L366 (HandleCommandOrbitAndSpeedChange); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L328</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L392 (TryApplyCommandTimeout); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L347</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L412 (GenerateTrajectorySetpointAndLandingGear); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L371</t>
+          <t>src/modules/flight_mode_manager/FlightModeManagerTest.cpp#L436 (StatusAndUsageFunctions); logs/priority_fix/functional-FlightModeManager.xml</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L113</t>
+          <t>src/lib/battery/BatteryTest.cpp#L118 (ParameterInitializationAndCellCount); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Voltage input: 1.5V (&lt; LITHIUM_BATTERY_RECOGNITION_VOLTAGE)</t>
+          <t>BAT1_CAPACITY=0 (unknown capacity); voltage input 1.5V (&lt; 2.1V recognition threshold); parameters and retained vehicle/flight-phase messages reset by fixture</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L125</t>
+          <t>src/lib/battery/BatteryTest.cpp#L131 (DisconnectedBatteryState); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L139</t>
+          <t>src/lib/battery/BatteryTest.cpp#L150 (ConnectedBatteryInitialTransition); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L160</t>
+          <t>src/lib/battery/BatteryTest.cpp#L173 (DetermineWarningLadder); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L176</t>
+          <t>src/lib/battery/BatteryTest.cpp#L191 (DetermineFaultsOvervoltage); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L194</t>
+          <t>src/lib/battery/BatteryTest.cpp#L209 (ComputeScaleThrustCompensation); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L217</t>
+          <t>src/lib/battery/BatteryTest.cpp#L236 (StateOfChargeVoltageBasedAndLoadDropCorrection); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L235</t>
+          <t>src/lib/battery/BatteryTest.cpp#L256 (StateOfChargeEstimationCoulombFusion); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L261</t>
+          <t>src/lib/battery/BatteryTest.cpp#L289 (ComputeRemainingTimeArmedAndFixedWing); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L302</t>
+          <t>src/lib/battery/BatteryTest.cpp#L338 (ExternalStateOfChargeOverride); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>src/lib/battery/BatteryTest.cpp#L313</t>
+          <t>src/lib/battery/BatteryTest.cpp#L350 (AnalogBatteryADCConversionAndChannels); logs/priority_fix/functional-Battery.xml</t>
         </is>
       </c>
     </row>
